--- a/artfynd/A 61830-2022 artfynd.xlsx
+++ b/artfynd/A 61830-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61830-2022 artfynd.xlsx
+++ b/artfynd/A 61830-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83669116</v>
+        <v>75952693</v>
       </c>
       <c r="B2" t="n">
-        <v>73697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,24 +703,20 @@
           <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ältsjön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664431.0866962528</v>
+        <v>664431</v>
       </c>
       <c r="R2" t="n">
-        <v>6640198.412620996</v>
+        <v>6640198</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,56 +741,43 @@
           <t>Almunge</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>F5EDF71A-2A65-402B-A038-57CFFD777A3B</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-02-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-11-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-02-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-11-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på grov hålek med savflöde</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
